--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="516">
   <si>
     <t>Reference</t>
   </si>
@@ -1490,6 +1490,84 @@
   </si>
   <si>
     <t>Extra</t>
+  </si>
+  <si>
+    <t>MOV</t>
+  </si>
+  <si>
+    <t>337-3343</t>
+  </si>
+  <si>
+    <t>MOV-07470K: Varistor, Metal oxide</t>
+  </si>
+  <si>
+    <t>Buck Convertor</t>
+  </si>
+  <si>
+    <t>300-7378</t>
+  </si>
+  <si>
+    <t>TPS56430YFDBT:DC/DC Convertor</t>
+  </si>
+  <si>
+    <t>R136927</t>
+  </si>
+  <si>
+    <t>22.1k Ohm 0805</t>
+  </si>
+  <si>
+    <t>Buck Resistor</t>
+  </si>
+  <si>
+    <t>R135252</t>
+  </si>
+  <si>
+    <t>88.7k Ohm</t>
+  </si>
+  <si>
+    <t>Buck Inductor</t>
+  </si>
+  <si>
+    <t>10uH</t>
+  </si>
+  <si>
+    <t>Buck Capacitor</t>
+  </si>
+  <si>
+    <t>R139414</t>
+  </si>
+  <si>
+    <t>22uF 10V 1206</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6</t>
+  </si>
+  <si>
+    <t>STM32</t>
+  </si>
+  <si>
+    <t>R139426</t>
+  </si>
+  <si>
+    <t>2.2uF 50V 1206</t>
+  </si>
+  <si>
+    <t>NPN Transistor</t>
+  </si>
+  <si>
+    <t>TIP31C</t>
+  </si>
+  <si>
+    <t>1(6)</t>
+  </si>
+  <si>
+    <t>PCB TSSOP</t>
+  </si>
+  <si>
+    <t>1(5)</t>
+  </si>
+  <si>
+    <t>tssop/soic/sop8/dip8</t>
   </si>
 </sst>
 </file>
@@ -2545,7 +2623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H47"/>
+  <dimension ref="A2:H57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -3480,6 +3558,176 @@
       </c>
       <c r="F47" t="s">
         <v>488</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>490</v>
+      </c>
+      <c r="C48" t="s">
+        <v>491</v>
+      </c>
+      <c r="D48" t="s">
+        <v>492</v>
+      </c>
+      <c r="E48">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>493</v>
+      </c>
+      <c r="C49" t="s">
+        <v>494</v>
+      </c>
+      <c r="D49" t="s">
+        <v>495</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>498</v>
+      </c>
+      <c r="C50" t="s">
+        <v>496</v>
+      </c>
+      <c r="D50" t="s">
+        <v>497</v>
+      </c>
+      <c r="E50">
+        <v>25</v>
+      </c>
+      <c r="F50" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>498</v>
+      </c>
+      <c r="C51" t="s">
+        <v>499</v>
+      </c>
+      <c r="D51" t="s">
+        <v>500</v>
+      </c>
+      <c r="E51">
+        <v>60</v>
+      </c>
+      <c r="F51" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>501</v>
+      </c>
+      <c r="C52">
+        <v>518868</v>
+      </c>
+      <c r="D52" t="s">
+        <v>502</v>
+      </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>503</v>
+      </c>
+      <c r="C53" t="s">
+        <v>504</v>
+      </c>
+      <c r="D53" t="s">
+        <v>505</v>
+      </c>
+      <c r="E53">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>507</v>
+      </c>
+      <c r="C54">
+        <v>31258</v>
+      </c>
+      <c r="D54" t="s">
+        <v>506</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>503</v>
+      </c>
+      <c r="C55" t="s">
+        <v>508</v>
+      </c>
+      <c r="D55" t="s">
+        <v>509</v>
+      </c>
+      <c r="E55">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>510</v>
+      </c>
+      <c r="C56">
+        <v>598820</v>
+      </c>
+      <c r="D56" t="s">
+        <v>511</v>
+      </c>
+      <c r="E56" t="s">
+        <v>512</v>
+      </c>
+      <c r="F56" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>513</v>
+      </c>
+      <c r="C57">
+        <v>1121328</v>
+      </c>
+      <c r="D57" t="s">
+        <v>515</v>
+      </c>
+      <c r="E57" t="s">
+        <v>514</v>
+      </c>
+      <c r="F57" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="543">
   <si>
     <t>Reference</t>
   </si>
@@ -1568,6 +1568,87 @@
   </si>
   <si>
     <t>tssop/soic/sop8/dip8</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Varistor</t>
+  </si>
+  <si>
+    <t>Standard Metal Oxide Varistor</t>
+  </si>
+  <si>
+    <t>RS Components</t>
+  </si>
+  <si>
+    <t>Ktron</t>
+  </si>
+  <si>
+    <t>Terminal Block</t>
+  </si>
+  <si>
+    <t>10(2/3)</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>1uF Capacitor</t>
+  </si>
+  <si>
+    <t>Female to Femal Connectror</t>
+  </si>
+  <si>
+    <t>1 Pack</t>
+  </si>
+  <si>
+    <t>171-4617594-7699533</t>
+  </si>
+  <si>
+    <t>171-5418070-3137137</t>
+  </si>
+  <si>
+    <t>171-4566669-5910707</t>
+  </si>
+  <si>
+    <t>Simcom A7672S</t>
+  </si>
+  <si>
+    <t>4G LTE Antenna</t>
+  </si>
+  <si>
+    <t>GPS Antenna Female Connector</t>
+  </si>
+  <si>
+    <t>RF Cable IPX to SMA Male</t>
+  </si>
+  <si>
+    <t>4G Module</t>
+  </si>
+  <si>
+    <t>GPS</t>
+  </si>
+  <si>
+    <t>RF Cable</t>
+  </si>
+  <si>
+    <t>Teminal Block</t>
+  </si>
+  <si>
+    <t>Cap</t>
+  </si>
+  <si>
+    <t>Female  to Female</t>
+  </si>
+  <si>
+    <t>R172593</t>
+  </si>
+  <si>
+    <t>R185622</t>
+  </si>
+  <si>
+    <t>R155458</t>
   </si>
 </sst>
 </file>
@@ -1651,7 +1732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1668,6 +1749,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2623,15 +2705,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H57"/>
+  <dimension ref="A2:I75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="65.28515625" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>121</v>
       </c>
@@ -2656,8 +2739,11 @@
       <c r="H2" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2676,8 +2762,11 @@
       <c r="F3" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2696,8 +2785,11 @@
       <c r="F4" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2713,8 +2805,11 @@
       <c r="F5" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2733,8 +2828,11 @@
       <c r="F6" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2753,8 +2851,11 @@
       <c r="F7" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2779,8 +2880,11 @@
       <c r="H8" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2799,8 +2903,11 @@
       <c r="F9" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2819,8 +2926,11 @@
       <c r="F10" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2839,8 +2949,11 @@
       <c r="F11" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2859,8 +2972,11 @@
       <c r="F12" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2879,8 +2995,11 @@
       <c r="F13" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2899,8 +3018,11 @@
       <c r="F14" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2919,8 +3041,11 @@
       <c r="F15" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2939,8 +3064,11 @@
       <c r="F16" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I16" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2959,8 +3087,11 @@
       <c r="F17" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I17" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2979,8 +3110,11 @@
       <c r="F18" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I18" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2999,8 +3133,11 @@
       <c r="F19" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I19" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -3019,8 +3156,11 @@
       <c r="F20" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I20" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -3039,8 +3179,11 @@
       <c r="F21" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I21" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3059,8 +3202,11 @@
       <c r="F22" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I22" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -3079,8 +3225,11 @@
       <c r="F23" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I23" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -3099,8 +3248,11 @@
       <c r="F24" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I24" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -3119,8 +3271,11 @@
       <c r="F25" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I25" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3139,8 +3294,11 @@
       <c r="F26" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I26" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3159,8 +3317,11 @@
       <c r="F27" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I27" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3179,8 +3340,11 @@
       <c r="F28" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I28" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3199,8 +3363,11 @@
       <c r="F29" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I29" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3219,8 +3386,11 @@
       <c r="F30" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I30" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3239,8 +3409,11 @@
       <c r="F31" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I31" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3259,8 +3432,11 @@
       <c r="F32" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I32" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3279,8 +3455,11 @@
       <c r="F33" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I33" s="10">
+        <v>45746</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3299,8 +3478,11 @@
       <c r="F34" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I34" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3319,8 +3501,11 @@
       <c r="F35" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I35" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3339,8 +3524,11 @@
       <c r="F36" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I36" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3359,8 +3547,11 @@
       <c r="F37" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I37" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3379,8 +3570,11 @@
       <c r="F38" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I38" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3399,8 +3593,11 @@
       <c r="F39" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I39" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3419,8 +3616,11 @@
       <c r="F40" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I40" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3439,8 +3639,11 @@
       <c r="F41" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I41" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3459,8 +3662,11 @@
       <c r="F42" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I42" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -3479,8 +3685,11 @@
       <c r="F43" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I43" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -3499,8 +3708,11 @@
       <c r="F44" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I44" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -3519,8 +3731,11 @@
       <c r="F45" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I45" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -3539,8 +3754,11 @@
       <c r="F46" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I46" s="10">
+        <v>45756</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
@@ -3559,8 +3777,14 @@
       <c r="F47" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I47" s="10">
+        <v>45762</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>46</v>
+      </c>
       <c r="B48" t="s">
         <v>490</v>
       </c>
@@ -3576,8 +3800,14 @@
       <c r="F48" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I48" s="10">
+        <v>45768</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>47</v>
+      </c>
       <c r="B49" t="s">
         <v>493</v>
       </c>
@@ -3593,8 +3823,14 @@
       <c r="F49" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I49" s="10">
+        <v>45768</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>48</v>
+      </c>
       <c r="B50" t="s">
         <v>498</v>
       </c>
@@ -3610,8 +3846,14 @@
       <c r="F50" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I50" s="10">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>49</v>
+      </c>
       <c r="B51" t="s">
         <v>498</v>
       </c>
@@ -3627,8 +3869,14 @@
       <c r="F51" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I51" s="10">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50</v>
+      </c>
       <c r="B52" t="s">
         <v>501</v>
       </c>
@@ -3644,8 +3892,14 @@
       <c r="F52" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I52" s="10">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>51</v>
+      </c>
       <c r="B53" t="s">
         <v>503</v>
       </c>
@@ -3661,8 +3915,14 @@
       <c r="F53" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I53" s="10">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>52</v>
+      </c>
       <c r="B54" t="s">
         <v>507</v>
       </c>
@@ -3678,8 +3938,14 @@
       <c r="F54" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I54" s="10">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>53</v>
+      </c>
       <c r="B55" t="s">
         <v>503</v>
       </c>
@@ -3695,8 +3961,14 @@
       <c r="F55" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I55" s="10">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>54</v>
+      </c>
       <c r="B56" t="s">
         <v>510</v>
       </c>
@@ -3712,8 +3984,14 @@
       <c r="F56" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="I56" s="10">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>55</v>
+      </c>
       <c r="B57" t="s">
         <v>513</v>
       </c>
@@ -3728,6 +4006,261 @@
       </c>
       <c r="F57" t="s">
         <v>308</v>
+      </c>
+      <c r="I57" s="10">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>517</v>
+      </c>
+      <c r="C58">
+        <v>2041839</v>
+      </c>
+      <c r="D58" t="s">
+        <v>518</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>519</v>
+      </c>
+      <c r="I58" s="10">
+        <v>45772</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>534</v>
+      </c>
+      <c r="C59">
+        <v>85437099</v>
+      </c>
+      <c r="D59" t="s">
+        <v>530</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>520</v>
+      </c>
+      <c r="I59" s="10">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>446</v>
+      </c>
+      <c r="C60">
+        <v>85291019</v>
+      </c>
+      <c r="D60" t="s">
+        <v>531</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>520</v>
+      </c>
+      <c r="I60" s="10">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>535</v>
+      </c>
+      <c r="C61">
+        <v>8529</v>
+      </c>
+      <c r="D61" t="s">
+        <v>532</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>520</v>
+      </c>
+      <c r="I61" s="10">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>536</v>
+      </c>
+      <c r="C62">
+        <v>85366990</v>
+      </c>
+      <c r="D62" t="s">
+        <v>533</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>520</v>
+      </c>
+      <c r="I62" s="10">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>537</v>
+      </c>
+      <c r="C63" t="s">
+        <v>528</v>
+      </c>
+      <c r="D63" t="s">
+        <v>521</v>
+      </c>
+      <c r="E63" t="s">
+        <v>522</v>
+      </c>
+      <c r="F63" t="s">
+        <v>523</v>
+      </c>
+      <c r="I63" s="10">
+        <v>45779</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>538</v>
+      </c>
+      <c r="C64" t="s">
+        <v>529</v>
+      </c>
+      <c r="D64" t="s">
+        <v>524</v>
+      </c>
+      <c r="E64">
+        <v>3</v>
+      </c>
+      <c r="F64" t="s">
+        <v>523</v>
+      </c>
+      <c r="I64" s="10">
+        <v>45779</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>539</v>
+      </c>
+      <c r="C65" t="s">
+        <v>527</v>
+      </c>
+      <c r="D65" t="s">
+        <v>525</v>
+      </c>
+      <c r="E65" t="s">
+        <v>526</v>
+      </c>
+      <c r="F65" t="s">
+        <v>523</v>
+      </c>
+      <c r="I65" s="10">
+        <v>45779</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="C66" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="C67" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="C68">
+        <v>162054</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="C69">
+        <v>1086490</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="C70">
+        <v>518879</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="C71" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
